--- a/outputs_xlsx_solution/test_new4.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/test_new4.4-wide-NC-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F2, F2, F3</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -675,7 +681,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -695,13 +701,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +727,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -747,13 +756,25 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -776,10 +797,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -799,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -811,10 +832,10 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -834,7 +855,10 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
@@ -846,10 +870,10 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -869,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -884,10 +908,10 @@
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +922,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -907,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
@@ -919,10 +943,10 @@
         <v>14</v>
       </c>
       <c r="O10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -933,7 +957,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -942,16 +966,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>14</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -971,16 +995,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
         <v>14</v>
       </c>
       <c r="N12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -991,7 +1015,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1000,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1020,7 +1044,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1029,16 +1053,16 @@
         <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1049,7 +1073,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1058,16 +1082,16 @@
         <v>9</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s">
         <v>14</v>
       </c>
       <c r="L15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1087,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
         <v>14</v>
@@ -1102,10 +1126,10 @@
         <v>14</v>
       </c>
       <c r="S16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1116,7 +1140,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" t="s">
         <v>5</v>
@@ -1125,7 +1149,7 @@
         <v>9</v>
       </c>
       <c r="N17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S17" t="s">
         <v>14</v>
@@ -1137,10 +1161,10 @@
         <v>14</v>
       </c>
       <c r="V17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1151,7 +1175,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
         <v>5</v>
@@ -1160,16 +1184,16 @@
         <v>9</v>
       </c>
       <c r="N18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O18" t="s">
         <v>14</v>
       </c>
       <c r="P18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1189,16 +1213,16 @@
         <v>9</v>
       </c>
       <c r="N19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" t="s">
         <v>14</v>
       </c>
       <c r="Q19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1209,7 +1233,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
         <v>5</v>
@@ -1218,16 +1242,16 @@
         <v>9</v>
       </c>
       <c r="O20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" t="s">
         <v>14</v>
       </c>
       <c r="Q20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1238,7 +1262,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M21" t="s">
         <v>5</v>
@@ -1247,16 +1271,19 @@
         <v>9</v>
       </c>
       <c r="O21" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>15</v>
       </c>
       <c r="R21" t="s">
         <v>14</v>
       </c>
       <c r="S21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1267,7 +1294,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
         <v>5</v>
@@ -1276,16 +1303,16 @@
         <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S22" t="s">
         <v>14</v>
       </c>
       <c r="T22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1305,7 +1332,13 @@
         <v>9</v>
       </c>
       <c r="P23" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>15</v>
+      </c>
+      <c r="R23" t="s">
+        <v>15</v>
       </c>
       <c r="S23" t="s">
         <v>14</v>
@@ -1320,10 +1353,10 @@
         <v>14</v>
       </c>
       <c r="W23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1334,7 +1367,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N24" t="s">
         <v>5</v>
@@ -1343,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W24" t="s">
         <v>14</v>
@@ -1355,10 +1388,10 @@
         <v>14</v>
       </c>
       <c r="Z24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1369,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N25" t="s">
         <v>5</v>
@@ -1378,16 +1411,16 @@
         <v>9</v>
       </c>
       <c r="P25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q25" t="s">
         <v>14</v>
       </c>
       <c r="R25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1407,19 +1440,19 @@
         <v>9</v>
       </c>
       <c r="P26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R26" t="s">
         <v>14</v>
       </c>
       <c r="S26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1430,7 +1463,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O27" t="s">
         <v>5</v>
@@ -1439,19 +1472,19 @@
         <v>9</v>
       </c>
       <c r="Q27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S27" t="s">
         <v>14</v>
       </c>
       <c r="T27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1462,7 +1495,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O28" t="s">
         <v>5</v>
@@ -1471,19 +1504,19 @@
         <v>9</v>
       </c>
       <c r="R28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T28" t="s">
         <v>14</v>
       </c>
       <c r="U28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1494,7 +1527,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
         <v>5</v>
@@ -1503,19 +1536,19 @@
         <v>9</v>
       </c>
       <c r="S29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U29" t="s">
         <v>14</v>
       </c>
       <c r="V29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1535,10 +1568,13 @@
         <v>9</v>
       </c>
       <c r="T30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U30" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="V30" t="s">
+        <v>15</v>
       </c>
       <c r="W30" t="s">
         <v>14</v>
@@ -1553,10 +1589,10 @@
         <v>14</v>
       </c>
       <c r="AA30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1567,7 +1603,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P31" t="s">
         <v>5</v>
@@ -1576,10 +1612,10 @@
         <v>9</v>
       </c>
       <c r="U31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s">
         <v>14</v>
@@ -1591,10 +1627,10 @@
         <v>14</v>
       </c>
       <c r="AD31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1605,7 +1641,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P32" t="s">
         <v>5</v>
@@ -1614,19 +1650,19 @@
         <v>9</v>
       </c>
       <c r="V32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X32" t="s">
         <v>14</v>
       </c>
       <c r="Y32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1646,19 +1682,19 @@
         <v>9</v>
       </c>
       <c r="W33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s">
         <v>14</v>
       </c>
       <c r="Z33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1669,7 +1705,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q34" t="s">
         <v>5</v>
@@ -1678,19 +1714,19 @@
         <v>9</v>
       </c>
       <c r="X34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s">
         <v>14</v>
       </c>
       <c r="AA34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1701,7 +1737,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q35" t="s">
         <v>5</v>
@@ -1710,19 +1746,19 @@
         <v>9</v>
       </c>
       <c r="Y35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s">
         <v>14</v>
       </c>
       <c r="AB35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1733,7 +1769,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q36" t="s">
         <v>5</v>
@@ -1742,19 +1778,19 @@
         <v>9</v>
       </c>
       <c r="Z36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB36" t="s">
         <v>14</v>
       </c>
       <c r="AC36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1774,10 +1810,10 @@
         <v>9</v>
       </c>
       <c r="AA37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC37" t="s">
         <v>14</v>
@@ -1792,10 +1828,10 @@
         <v>14</v>
       </c>
       <c r="AG37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1806,7 +1842,7 @@
         <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R38" t="s">
         <v>5</v>
@@ -1815,10 +1851,10 @@
         <v>9</v>
       </c>
       <c r="AB38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG38" t="s">
         <v>14</v>
@@ -1830,10 +1866,10 @@
         <v>14</v>
       </c>
       <c r="AJ38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1844,7 +1880,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R39" t="s">
         <v>5</v>
@@ -1853,19 +1889,19 @@
         <v>9</v>
       </c>
       <c r="AC39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE39" t="s">
         <v>14</v>
       </c>
       <c r="AF39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1885,19 +1921,19 @@
         <v>9</v>
       </c>
       <c r="AD40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF40" t="s">
         <v>14</v>
       </c>
       <c r="AG40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -1908,7 +1944,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S41" t="s">
         <v>5</v>
@@ -1917,19 +1953,19 @@
         <v>9</v>
       </c>
       <c r="AE41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG41" t="s">
         <v>14</v>
       </c>
       <c r="AH41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1940,7 +1976,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S42" t="s">
         <v>5</v>
@@ -1949,19 +1985,19 @@
         <v>9</v>
       </c>
       <c r="AF42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH42" t="s">
         <v>14</v>
       </c>
       <c r="AI42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1972,7 +2008,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S43" t="s">
         <v>5</v>
@@ -1981,19 +2017,19 @@
         <v>9</v>
       </c>
       <c r="AG43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI43" t="s">
         <v>14</v>
       </c>
       <c r="AJ43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -2004,7 +2040,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ44" t="s">
         <v>5</v>
@@ -2013,21 +2049,21 @@
         <v>9</v>
       </c>
       <c r="AL44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM44" t="s">
         <v>14</v>
       </c>
       <c r="AN44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
@@ -2035,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -2043,15 +2079,15 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -2059,39 +2095,55 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
         <v>35</v>
       </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
         <v>36</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
